--- a/จำนวนประชากรรายจังหวัด.xlsx
+++ b/จำนวนประชากรรายจังหวัด.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5A74E8-5F14-FF42-925A-1E110542F5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF1EB08-AB34-264D-BAEE-6350687E7523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12240" yWindow="740" windowWidth="16480" windowHeight="17160" firstSheet="1" activeTab="4" xr2:uid="{B583505E-6B9D-6A43-8DEA-B19707295A06}"/>
+    <workbookView xWindow="12240" yWindow="740" windowWidth="16480" windowHeight="17140" activeTab="2" xr2:uid="{B583505E-6B9D-6A43-8DEA-B19707295A06}"/>
   </bookViews>
   <sheets>
     <sheet name="จำนวนประชากร2563" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="81">
   <si>
     <t>รหัสจังหวัด</t>
   </si>
@@ -283,21 +283,31 @@
   </si>
   <si>
     <t>จำนวนประชากรทั้งหมด</t>
-  </si>
-  <si>
-    <t>จำนวนประชากรชาย</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -321,8 +331,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2434,8 +2446,8 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>81</v>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2445,8 +2457,8 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>32270615</v>
+      <c r="C2" s="2">
+        <v>66090475</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2456,8 +2468,8 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3">
-        <v>2571974</v>
+      <c r="C3" s="2">
+        <v>5494932</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2467,8 +2479,8 @@
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4">
-        <v>646798</v>
+      <c r="C4" s="2">
+        <v>1360227</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2478,8 +2490,8 @@
       <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>601682</v>
+      <c r="C5" s="2">
+        <v>1295916</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2489,8 +2501,8 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6">
-        <v>568877</v>
+      <c r="C6" s="2">
+        <v>1201532</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2500,8 +2512,8 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7">
-        <v>393685</v>
+      <c r="C7" s="2">
+        <v>820417</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2511,8 +2523,8 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8">
-        <v>130337</v>
+      <c r="C8" s="2">
+        <v>272587</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2522,8 +2534,8 @@
       <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C9">
-        <v>366294</v>
+      <c r="C9" s="2">
+        <v>735293</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2533,8 +2545,8 @@
       <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="C10">
-        <v>96345</v>
+      <c r="C10" s="2">
+        <v>202797</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2544,8 +2556,8 @@
       <c r="B11" t="s">
         <v>11</v>
       </c>
-      <c r="C11">
-        <v>152800</v>
+      <c r="C11" s="2">
+        <v>318308</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2555,8 +2567,8 @@
       <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12">
-        <v>313213</v>
+      <c r="C12" s="2">
+        <v>638582</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2566,8 +2578,8 @@
       <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C13">
-        <v>777220</v>
+      <c r="C13" s="2">
+        <v>1594758</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2577,8 +2589,8 @@
       <c r="B14" t="s">
         <v>14</v>
       </c>
-      <c r="C14">
-        <v>372863</v>
+      <c r="C14" s="2">
+        <v>759386</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2588,8 +2600,8 @@
       <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C15">
-        <v>261874</v>
+      <c r="C15" s="2">
+        <v>536144</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2599,8 +2611,8 @@
       <c r="B16" t="s">
         <v>16</v>
       </c>
-      <c r="C16">
-        <v>112668</v>
+      <c r="C16" s="2">
+        <v>227808</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2610,8 +2622,8 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17">
-        <v>355759</v>
+      <c r="C17" s="2">
+        <v>726687</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -2621,8 +2633,8 @@
       <c r="B18" t="s">
         <v>18</v>
       </c>
-      <c r="C18">
-        <v>245884</v>
+      <c r="C18" s="2">
+        <v>497778</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2632,8 +2644,8 @@
       <c r="B19" t="s">
         <v>19</v>
       </c>
-      <c r="C19">
-        <v>128790</v>
+      <c r="C19" s="2">
+        <v>260406</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2643,8 +2655,8 @@
       <c r="B20" t="s">
         <v>20</v>
       </c>
-      <c r="C20">
-        <v>281252</v>
+      <c r="C20" s="2">
+        <v>562816</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2654,8 +2666,8 @@
       <c r="B21" t="s">
         <v>21</v>
       </c>
-      <c r="C21">
-        <v>1290253</v>
+      <c r="C21" s="2">
+        <v>2630058</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2665,8 +2677,8 @@
       <c r="B22" t="s">
         <v>22</v>
       </c>
-      <c r="C22">
-        <v>781530</v>
+      <c r="C22" s="2">
+        <v>1576915</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2676,8 +2688,8 @@
       <c r="B23" t="s">
         <v>23</v>
       </c>
-      <c r="C23">
-        <v>682371</v>
+      <c r="C23" s="2">
+        <v>1372910</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2687,8 +2699,8 @@
       <c r="B24" t="s">
         <v>24</v>
       </c>
-      <c r="C24">
-        <v>723755</v>
+      <c r="C24" s="2">
+        <v>1454730</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2698,8 +2710,8 @@
       <c r="B25" t="s">
         <v>25</v>
       </c>
-      <c r="C25">
-        <v>932120</v>
+      <c r="C25" s="2">
+        <v>1869806</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -2709,8 +2721,8 @@
       <c r="B26" t="s">
         <v>26</v>
       </c>
-      <c r="C26">
-        <v>264756</v>
+      <c r="C26" s="2">
+        <v>531599</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2720,8 +2732,8 @@
       <c r="B27" t="s">
         <v>27</v>
       </c>
-      <c r="C27">
-        <v>551407</v>
+      <c r="C27" s="2">
+        <v>1117925</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2731,8 +2743,8 @@
       <c r="B28" t="s">
         <v>28</v>
       </c>
-      <c r="C28">
-        <v>186594</v>
+      <c r="C28" s="2">
+        <v>375382</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2742,8 +2754,8 @@
       <c r="B29" t="s">
         <v>29</v>
       </c>
-      <c r="C29">
-        <v>211158</v>
+      <c r="C29" s="2">
+        <v>421684</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2753,8 +2765,8 @@
       <c r="B30" t="s">
         <v>30</v>
       </c>
-      <c r="C30">
-        <v>253342</v>
+      <c r="C30" s="2">
+        <v>508325</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -2764,8 +2776,8 @@
       <c r="B31" t="s">
         <v>31</v>
       </c>
-      <c r="C31">
-        <v>876082</v>
+      <c r="C31" s="2">
+        <v>1784641</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2775,8 +2787,8 @@
       <c r="B32" t="s">
         <v>32</v>
       </c>
-      <c r="C32">
-        <v>772344</v>
+      <c r="C32" s="2">
+        <v>1563048</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2786,8 +2798,8 @@
       <c r="B33" t="s">
         <v>33</v>
       </c>
-      <c r="C33">
-        <v>319099</v>
+      <c r="C33" s="2">
+        <v>637341</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2797,8 +2809,8 @@
       <c r="B34" t="s">
         <v>34</v>
       </c>
-      <c r="C34">
-        <v>255393</v>
+      <c r="C34" s="2">
+        <v>515795</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2808,8 +2820,8 @@
       <c r="B35" t="s">
         <v>35</v>
       </c>
-      <c r="C35">
-        <v>462896</v>
+      <c r="C35" s="2">
+        <v>944605</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -2819,8 +2831,8 @@
       <c r="B36" t="s">
         <v>36</v>
       </c>
-      <c r="C36">
-        <v>639009</v>
+      <c r="C36" s="2">
+        <v>1291131</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -2830,8 +2842,8 @@
       <c r="B37" t="s">
         <v>37</v>
       </c>
-      <c r="C37">
-        <v>479874</v>
+      <c r="C37" s="2">
+        <v>972101</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -2841,8 +2853,8 @@
       <c r="B38" t="s">
         <v>38</v>
       </c>
-      <c r="C38">
-        <v>568553</v>
+      <c r="C38" s="2">
+        <v>1145187</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -2852,8 +2864,8 @@
       <c r="B39" t="s">
         <v>39</v>
       </c>
-      <c r="C39">
-        <v>356834</v>
+      <c r="C39" s="2">
+        <v>716647</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -2863,8 +2875,8 @@
       <c r="B40" t="s">
         <v>40</v>
       </c>
-      <c r="C40">
-        <v>175542</v>
+      <c r="C40" s="2">
+        <v>351588</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -2874,8 +2886,8 @@
       <c r="B41" t="s">
         <v>41</v>
       </c>
-      <c r="C41">
-        <v>864339</v>
+      <c r="C41" s="2">
+        <v>1792474</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -2885,8 +2897,8 @@
       <c r="B42" t="s">
         <v>42</v>
       </c>
-      <c r="C42">
-        <v>191596</v>
+      <c r="C42" s="2">
+        <v>399557</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -2896,8 +2908,8 @@
       <c r="B43" t="s">
         <v>43</v>
       </c>
-      <c r="C43">
-        <v>349574</v>
+      <c r="C43" s="2">
+        <v>718790</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -2907,8 +2919,8 @@
       <c r="B44" t="s">
         <v>44</v>
       </c>
-      <c r="C44">
-        <v>215648</v>
+      <c r="C44" s="2">
+        <v>442949</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -2918,8 +2930,8 @@
       <c r="B45" t="s">
         <v>45</v>
       </c>
-      <c r="C45">
-        <v>207174</v>
+      <c r="C45" s="2">
+        <v>430669</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -2929,8 +2941,8 @@
       <c r="B46" t="s">
         <v>46</v>
       </c>
-      <c r="C46">
-        <v>236941</v>
+      <c r="C46" s="2">
+        <v>474539</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -2940,8 +2952,8 @@
       <c r="B47" t="s">
         <v>47</v>
       </c>
-      <c r="C47">
-        <v>224063</v>
+      <c r="C47" s="2">
+        <v>461431</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -2951,8 +2963,8 @@
       <c r="B48" t="s">
         <v>48</v>
       </c>
-      <c r="C48">
-        <v>630619</v>
+      <c r="C48" s="2">
+        <v>1299636</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -2962,8 +2974,8 @@
       <c r="B49" t="s">
         <v>49</v>
       </c>
-      <c r="C49">
-        <v>145194</v>
+      <c r="C49" s="2">
+        <v>286786</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -2973,8 +2985,8 @@
       <c r="B50" t="s">
         <v>50</v>
       </c>
-      <c r="C50">
-        <v>501235</v>
+      <c r="C50" s="2">
+        <v>1028814</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -2984,8 +2996,8 @@
       <c r="B51" t="s">
         <v>51</v>
       </c>
-      <c r="C51">
-        <v>158139</v>
+      <c r="C51" s="2">
+        <v>323860</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -2995,8 +3007,8 @@
       <c r="B52" t="s">
         <v>52</v>
       </c>
-      <c r="C52">
-        <v>349696</v>
+      <c r="C52" s="2">
+        <v>708775</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -3006,8 +3018,8 @@
       <c r="B53" t="s">
         <v>53</v>
       </c>
-      <c r="C53">
-        <v>345732</v>
+      <c r="C53" s="2">
+        <v>684140</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -3017,8 +3029,8 @@
       <c r="B54" t="s">
         <v>54</v>
       </c>
-      <c r="C54">
-        <v>281413</v>
+      <c r="C54" s="2">
+        <v>581652</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -3028,8 +3040,8 @@
       <c r="B55" t="s">
         <v>55</v>
       </c>
-      <c r="C55">
-        <v>412742</v>
+      <c r="C55" s="2">
+        <v>844494</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -3039,8 +3051,8 @@
       <c r="B56" t="s">
         <v>56</v>
       </c>
-      <c r="C56">
-        <v>256341</v>
+      <c r="C56" s="2">
+        <v>525944</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -3050,8 +3062,8 @@
       <c r="B57" t="s">
         <v>57</v>
       </c>
-      <c r="C57">
-        <v>479134</v>
+      <c r="C57" s="2">
+        <v>973386</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -3061,8 +3073,8 @@
       <c r="B58" t="s">
         <v>58</v>
       </c>
-      <c r="C58">
-        <v>420322</v>
+      <c r="C58" s="2">
+        <v>865807</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -3072,8 +3084,8 @@
       <c r="B59" t="s">
         <v>59</v>
       </c>
-      <c r="C59">
-        <v>448109</v>
+      <c r="C59" s="2">
+        <v>894283</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -3083,8 +3095,8 @@
       <c r="B60" t="s">
         <v>60</v>
       </c>
-      <c r="C60">
-        <v>400366</v>
+      <c r="C60" s="2">
+        <v>830695</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -3094,8 +3106,8 @@
       <c r="B61" t="s">
         <v>61</v>
       </c>
-      <c r="C61">
-        <v>442350</v>
+      <c r="C61" s="2">
+        <v>921882</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -3105,8 +3117,8 @@
       <c r="B62" t="s">
         <v>62</v>
       </c>
-      <c r="C62">
-        <v>283474</v>
+      <c r="C62" s="2">
+        <v>589428</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -3116,8 +3128,8 @@
       <c r="B63" t="s">
         <v>63</v>
       </c>
-      <c r="C63">
-        <v>90381</v>
+      <c r="C63" s="2">
+        <v>189453</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -3127,8 +3139,8 @@
       <c r="B64" t="s">
         <v>64</v>
       </c>
-      <c r="C64">
-        <v>232601</v>
+      <c r="C64" s="2">
+        <v>482950</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -3138,8 +3150,8 @@
       <c r="B65" t="s">
         <v>65</v>
       </c>
-      <c r="C65">
-        <v>273525</v>
+      <c r="C65" s="2">
+        <v>553298</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -3149,8 +3161,8 @@
       <c r="B66" t="s">
         <v>66</v>
       </c>
-      <c r="C66">
-        <v>762647</v>
+      <c r="C66" s="2">
+        <v>1545147</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -3160,8 +3172,8 @@
       <c r="B67" t="s">
         <v>67</v>
       </c>
-      <c r="C67">
-        <v>238455</v>
+      <c r="C67" s="2">
+        <v>480057</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -3171,8 +3183,8 @@
       <c r="B68" t="s">
         <v>68</v>
       </c>
-      <c r="C68">
-        <v>133459</v>
+      <c r="C68" s="2">
+        <v>267442</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -3182,8 +3194,8 @@
       <c r="B69" t="s">
         <v>69</v>
       </c>
-      <c r="C69">
-        <v>197101</v>
+      <c r="C69" s="2">
+        <v>417891</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -3193,8 +3205,8 @@
       <c r="B70" t="s">
         <v>70</v>
       </c>
-      <c r="C70">
-        <v>527555</v>
+      <c r="C70" s="2">
+        <v>1073663</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -3204,8 +3216,8 @@
       <c r="B71" t="s">
         <v>71</v>
       </c>
-      <c r="C71">
-        <v>97803</v>
+      <c r="C71" s="2">
+        <v>194226</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -3215,8 +3227,8 @@
       <c r="B72" t="s">
         <v>72</v>
       </c>
-      <c r="C72">
-        <v>251226</v>
+      <c r="C72" s="2">
+        <v>509385</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -3226,8 +3238,8 @@
       <c r="B73" t="s">
         <v>73</v>
       </c>
-      <c r="C73">
-        <v>696482</v>
+      <c r="C73" s="2">
+        <v>1431063</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -3237,8 +3249,8 @@
       <c r="B74" t="s">
         <v>74</v>
       </c>
-      <c r="C74">
-        <v>161878</v>
+      <c r="C74" s="2">
+        <v>325303</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -3248,8 +3260,8 @@
       <c r="B75" t="s">
         <v>75</v>
       </c>
-      <c r="C75">
-        <v>311849</v>
+      <c r="C75" s="2">
+        <v>638206</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -3259,8 +3271,8 @@
       <c r="B76" t="s">
         <v>76</v>
       </c>
-      <c r="C76">
-        <v>253817</v>
+      <c r="C76" s="2">
+        <v>521619</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -3270,8 +3282,8 @@
       <c r="B77" t="s">
         <v>77</v>
       </c>
-      <c r="C77">
-        <v>362263</v>
+      <c r="C77" s="2">
+        <v>732955</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -3281,8 +3293,8 @@
       <c r="B78" t="s">
         <v>78</v>
       </c>
-      <c r="C78">
-        <v>271480</v>
+      <c r="C78" s="2">
+        <v>545913</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -3292,8 +3304,8 @@
       <c r="B79" t="s">
         <v>79</v>
       </c>
-      <c r="C79">
-        <v>402665</v>
+      <c r="C79" s="2">
+        <v>814121</v>
       </c>
     </row>
   </sheetData>
